--- a/data/daily/2026-09/2026-09-08.xlsx
+++ b/data/daily/2026-09/2026-09-08.xlsx
@@ -1220,14 +1220,39 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1267,67 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,17 +1342,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,110 +1367,35 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1475,52 +1475,127 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1528,129 +1603,54 @@
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -3151,7 +3151,7 @@
     <row r="20" ht="38" customHeight="1">
       <c r="B20" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3159,34 +3159,34 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7556791</t>
+          <t>https://gift.kakao.com/product/12064702</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
         </is>
       </c>
     </row>
     <row r="21" ht="38" customHeight="1">
       <c r="B21" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3194,27 +3194,27 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>33,200원</t>
+          <t>25,900원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12064702</t>
+          <t>https://gift.kakao.com/product/7556791</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
         </is>
       </c>
     </row>
@@ -3728,12 +3728,12 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -3785,12 +3785,12 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
+          <t>알디콤</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
           <t>익스트림</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>알디콤</t>
         </is>
       </c>
     </row>
@@ -3842,12 +3842,12 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
           <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
     </row>
@@ -3899,12 +3899,12 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
+          <t>33,200원</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
           <t>25,900원</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>33,200원</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>휴럼 하루한포 6년근 고려홍삼 5포 5일분</t>
+          <t>휴럼 하루한알 6년근 고려 홍삼환 9환 9일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4072,24 +4072,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157053&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157095&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260327/PrU3TzDbYVJKWXoKyRxC919157053_00_01PrU3TzDbYVJKWXoKyRxC.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260826/gxSEg0bfLulOAScPenvi919157095_00_01gxSEg0bfLulOAScPenvi.jpg</t>
         </is>
       </c>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4097,34 +4097,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
+          <t>자연관 바이탈 밀크씨슬＆비타민B 4병</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602146&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20251211/MXX9ubQFCqeb0HoGBeRC613602146_00_01MXX9ubQFCqeb0HoGBeRC.jpg</t>
         </is>
       </c>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4132,12 +4132,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[보령약국 X Pantio] 다이어트 컷 올인원 15포 15일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>판티오</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4147,19 +4147,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=033991021&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260805/xVYROwLnuZYLoqWwcjU6033991021_00_00xVYROwLnuZYLoqWwcjU6.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4167,34 +4167,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>유한양행 프레쉬츄 생유산균 30정 30일분</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651651&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260325/Mz4AWbpywwVFSrdyow4Z600651651_00_00Mz4AWbpywwVFSrdyow4Z.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4212,24 +4212,24 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000132&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000136&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/SvY5chCvz0QZIyP7AdTc600000132_00_00SvY5chCvz0QZIyP7AdTc.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5KgtE2Z5pfS6P1gIBIIh600000136_00_005KgtE2Z5pfS6P1gIBIIh.png</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[홍삼입문자] 자연관 6년근 홍삼정 에너타임 스탠다드 14포 14일분</t>
+          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=901762105&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=985472642&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260612/6YtHsleJV0YMOtFdtOAk901762105_00_016YtHsleJV0YMOtFdtOAk.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250623/yivvMAKVS3Hyi026FPyX985472642_00_00yivvMAKVS3Hyi026FPyX.jpg</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
+          <t>휴럼 하루한알 침향환 9환 9일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>휴럼</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -4287,19 +4287,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157094&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260826/o7EiJdX7BYMCuTvEmVmE919157094_00_01o7EiJdX7BYMCuTvEmVmE.jpg</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대웅제약 콘드로이친 30정 30일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4317,17 +4317,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000152&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/b7btdcjQN0UwyzjBmHvY600000152_00_00b7btdcjQN0UwyzjBmHvY.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4377,27 +4377,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
         </is>
       </c>
     </row>
@@ -4517,47 +4517,47 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>비타민D</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>홍삼/인삼</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>마그네슘</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
     </row>
@@ -4574,19 +4574,19 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>자연관</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>판티오</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>유한양행</t>
-        </is>
-      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
@@ -4594,27 +4594,27 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>휴럼</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
           <t>이너뷰 바이 리튠</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
         </is>
       </c>
     </row>
@@ -4626,52 +4626,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>휴럼 하루한포 6년근 고려홍삼 5포 5일분</t>
+          <t>휴럼 하루한알 6년근 고려 홍삼환 9환 9일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>자연관 바이탈 밀크씨슬＆비타민B 4병</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>[보령약국 X Pantio] 다이어트 컷 올인원 15포 15일분</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>유한양행 프레쉬츄 생유산균 30정 30일분</t>
-        </is>
-      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>[홍삼입문자] 자연관 6년근 홍삼정 에너타임 스탠다드 14포 14일분</t>
+          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
+          <t>휴럼 하루한알 침향환 9환 9일분</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 마그네슘 30정 30일분</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
           <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 콘드로이친 30정 30일분</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 마그네슘 30정 30일분</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
     </row>
@@ -4683,52 +4683,52 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
           <t>2,000원</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>2,000원</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
         </is>
       </c>
     </row>
@@ -4875,27 +4875,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>닥터아돌 카테킨 아세로라CD 60정 (+시나모롤키링)/위디어트 히카바이오틱스 하이드록시 시트르산 21포</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>닥터아돌</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>21,900원</t>
+          <t>14,900원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000237815&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023781533ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355480ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4910,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[9월 올영픽/품절대란] 닥터아돌 카테킨 아세로라 칼시페롤 C D 60정 (+시나모롤 틴케이스 키링)</t>
+          <t>닥터아돌 카테킨 아세로라CD 60정 (+시나모롤키링)/위디어트 히카바이오틱스 하이드록시 시트르산 21포</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4925,19 +4925,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000218073&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000237815&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021807373ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023781533ko.png?l=ko</t>
         </is>
       </c>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4945,34 +4945,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14,900원</t>
+          <t>10,900원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000164736&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355480ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0016/A00000016473622ko.png?l=ko</t>
         </is>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4980,34 +4980,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>락토핏 골드 트리플 기획 (3개월분)</t>
+          <t>[9월 올영픽] 고려은단 메가도스C 비타민C 3000mg 30포 (+헬로키티 파우치)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>락토핏</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>21,900원</t>
+          <t>9,900원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000199062&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000187268&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019906245ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018726811ko.png?l=ko</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5015,34 +5015,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[9월 올영픽] 고려은단 메가도스C 비타민C 3000mg 30포 (+헬로키티 파우치)</t>
+          <t>[수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>대원제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9,900원</t>
+          <t>18,900원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000187268&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247884&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018726811ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024788471ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5050,34 +5050,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>락토핏 골드 트리플 기획 (3개월분)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>락토핏</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>39,800원</t>
+          <t>21,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000199062&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019906245ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5085,34 +5085,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[9월 올영픽] 콜레올로지 컷 다이어트 유산균 14캡슐 (+마이멜로디 카라비너) (10일분) / 20캡슐</t>
+          <t>[골라담기/신제품] 멜라메이트 구미 타트체리맛/리치백도맛/애플민트맛/2mg 구미</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>7,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000229934&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000218546&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022993425ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021854632ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5120,34 +5120,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>13,950원</t>
+          <t>31,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014345ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5155,34 +5155,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>55,900원</t>
+          <t>39,800원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308652ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5190,27 +5190,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
+          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 10종 택 1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>씨제이웰케어</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18,400원</t>
+          <t>5,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364587ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786106ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -5335,42 +5335,42 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -5382,52 +5382,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>멜라메이트</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>닥터아돌</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>닥터아돌</t>
-        </is>
-      </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>대원제약</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>락토핏</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>멜라메이트</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>락토핏</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>고려은단</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>프로뉴트리션</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>푸드올로지</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>바이오코어유산균</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>씨제이웰케어</t>
         </is>
       </c>
     </row>
@@ -5439,52 +5439,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>닥터아돌 카테킨 아세로라CD 60정 (+시나모롤키링)/위디어트 히카바이오틱스 하이드록시 시트르산 21포</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>[9월 올영픽/품절대란] 닥터아돌 카테킨 아세로라 칼시페롤 C D 60정 (+시나모롤 틴케이스 키링)</t>
-        </is>
-      </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
+          <t>[9월 올영픽] 고려은단 메가도스C 비타민C 3000mg 30포 (+헬로키티 파우치)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>[수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
           <t>락토핏 골드 트리플 기획 (3개월분)</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>[9월 올영픽] 고려은단 메가도스C 비타민C 3000mg 30포 (+헬로키티 파우치)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>[골라담기/신제품] 멜라메이트 구미 타트체리맛/리치백도맛/애플민트맛/2mg 구미</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[9월 올영픽] 콜레올로지 컷 다이어트 유산균 14캡슐 (+마이멜로디 카라비너) (10일분) / 20캡슐</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
-        </is>
-      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
+          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 10종 택 1</t>
         </is>
       </c>
     </row>
@@ -5496,52 +5496,52 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
+          <t>14,900원</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
           <t>21,900원</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>10,900원</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>9,900원</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>18,900원</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>21,900원</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>14,900원</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>21,900원</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>9,900원</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>7,900원</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>31,900원</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>39,800원</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>18,900원</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>13,950원</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>55,900원</t>
-        </is>
-      </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>18,400원</t>
+          <t>5,900원</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -5677,32 +5677,32 @@
         <v>35</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>22.5</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -5711,61 +5711,61 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>22.5</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
         <v>2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
         <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -5777,7 +5777,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5799,7 +5799,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5809,10 +5809,10 @@
         <v>2.5</v>
       </c>
       <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
         <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5831,19 +5831,19 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5856,10 +5856,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
         <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/daily/2026-09/2026-09-08.xlsx
+++ b/data/daily/2026-09/2026-09-08.xlsx
@@ -1245,14 +1245,39 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,17 +1292,67 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,17 +1367,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1317,85 +1392,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1500,52 +1500,127 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1553,104 +1628,29 @@
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
     <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2470,7 +2470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2517,6 +2517,46 @@
           <t>이미지URL</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>리뷰평점</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>리뷰건수</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>긍정1</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>긍정2</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>긍정3</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>부정1</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>부정2</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>부정3</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
@@ -2552,6 +2592,18 @@
           <t>https://st.kakaocdn.net/product/gift/product/20260831092457_c9ec264b75c847a2a3e6db3fc0b1959c.jpg</t>
         </is>
       </c>
+      <c r="I2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J2" t="n">
+        <v>15990</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
@@ -2587,6 +2639,18 @@
           <t>https://st.kakaocdn.net/product/gift/product/20260907094243_6872802604f04e1aad5886d9e457af18.jpg</t>
         </is>
       </c>
+      <c r="I3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>15326</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
@@ -2622,6 +2686,18 @@
           <t>https://st.kakaocdn.net/product/gift/product/20260907082858_3910675c66b1495890273ec4879739ea.jpg</t>
         </is>
       </c>
+      <c r="I4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3340</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
@@ -2657,6 +2733,18 @@
           <t>https://st.kakaocdn.net/product/gift/product/20260901110153_bb9a8b1870e2492e99dbbf1747444c66.jpg</t>
         </is>
       </c>
+      <c r="I5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6447</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
@@ -2692,6 +2780,18 @@
           <t>https://st.kakaocdn.net/product/gift/product/20260219100848_1c2cc8073bd44eaab9f09d6b8fb8f34c.jpg</t>
         </is>
       </c>
+      <c r="I6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8686</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
@@ -2727,6 +2827,18 @@
           <t>https://st.kakaocdn.net/product/gift/product/20260601193534_8d89165f65364cb0b3c77a98481c17d6.jpg</t>
         </is>
       </c>
+      <c r="I7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>711</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
@@ -2762,6 +2874,18 @@
           <t>https://st.kakaocdn.net/product/gift/product/20260812135521_25667cc1efc34a698d1813fe75189344.jpg</t>
         </is>
       </c>
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1611</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
@@ -2797,6 +2921,18 @@
           <t>https://st.kakaocdn.net/product/gift/product/20260831093017_c95c591e7b5b4e3d9e549888b299930a.jpg</t>
         </is>
       </c>
+      <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>773</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
@@ -2832,6 +2968,18 @@
           <t>https://st.kakaocdn.net/product/gift/product/20260513082713_f5025425b9024348b2621639f67a34af.jpg</t>
         </is>
       </c>
+      <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2607</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
@@ -2867,6 +3015,18 @@
           <t>https://st.kakaocdn.net/product/gift/product/20260907084156_6695f5fa3b10400983a93ac3be43afb0.jpg</t>
         </is>
       </c>
+      <c r="I11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>766</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12" ht="38" customHeight="1">
       <c r="B12" t="inlineStr">
@@ -2902,6 +3062,18 @@
           <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
         </is>
       </c>
+      <c r="I12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>49</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13" ht="38" customHeight="1">
       <c r="B13" t="inlineStr">
@@ -2937,6 +3109,18 @@
           <t>https://st.kakaocdn.net/product/gift/product/20260907091018_68a44d5ed50249e7aa6ad05f30d0e480.jpg</t>
         </is>
       </c>
+      <c r="I13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>729</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14" ht="38" customHeight="1">
       <c r="B14" t="inlineStr">
@@ -2972,6 +3156,18 @@
           <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
         </is>
       </c>
+      <c r="I14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>142</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15" ht="38" customHeight="1">
       <c r="B15" t="inlineStr">
@@ -3007,6 +3203,18 @@
           <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
         </is>
       </c>
+      <c r="I15" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>213</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16" ht="38" customHeight="1">
       <c r="B16" t="inlineStr">
@@ -3042,6 +3250,18 @@
           <t>https://st.kakaocdn.net/product/gift/product/20260831160758_47e2ca88a3ec4835979cf9737a40b276.jpg</t>
         </is>
       </c>
+      <c r="I16" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1653</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17" ht="38" customHeight="1">
       <c r="B17" t="inlineStr">
@@ -3077,6 +3297,18 @@
           <t>https://st.kakaocdn.net/product/gift/product/20260701120356_f9d975374d374b858dd4262325030e55.jpg</t>
         </is>
       </c>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1894</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18" ht="38" customHeight="1">
       <c r="B18" t="inlineStr">
@@ -3112,6 +3344,18 @@
           <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
         </is>
       </c>
+      <c r="I18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>247</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19" ht="38" customHeight="1">
       <c r="B19" t="inlineStr">
@@ -3147,11 +3391,23 @@
           <t>https://st.kakaocdn.net/product/gift/product/20260727151443_bd470867f85f4a79857e43d8b82ff835.jpg</t>
         </is>
       </c>
+      <c r="I19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>38</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20" ht="38" customHeight="1">
       <c r="B20" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3159,34 +3415,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>33,200원</t>
+          <t>25,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12064702</t>
+          <t>https://gift.kakao.com/product/7556791</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
-        </is>
-      </c>
+          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1534</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21" ht="38" customHeight="1">
       <c r="B21" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3194,29 +3462,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7556791</t>
+          <t>https://gift.kakao.com/product/12064702</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
-        </is>
-      </c>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3728,12 +4008,12 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
     </row>
@@ -3785,12 +4065,12 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
           <t>알디콤</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>익스트림</t>
         </is>
       </c>
     </row>
@@ -3842,12 +4122,12 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
+          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
           <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
     </row>
@@ -3899,12 +4179,12 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
+          <t>25,900원</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
           <t>33,200원</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>25,900원</t>
         </is>
       </c>
     </row>
@@ -4003,7 +4283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4050,6 +4330,46 @@
           <t>이미지URL</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>리뷰평점</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>리뷰건수</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>긍정1</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>긍정2</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>긍정3</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>부정1</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>부정2</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>부정3</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
@@ -4062,7 +4382,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>휴럼 하루한알 6년근 고려 홍삼환 9환 9일분</t>
+          <t>휴럼 하루한포 6년근 고려홍삼 5포 5일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4072,24 +4392,38 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157095&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157053&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260826/gxSEg0bfLulOAScPenvi919157095_00_01gxSEg0bfLulOAScPenvi.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260327/PrU3TzDbYVJKWXoKyRxC919157053_00_01PrU3TzDbYVJKWXoKyRxC.jpg</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>621</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4097,34 +4431,48 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>자연관 바이탈 밀크씨슬＆비타민B 4병</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602146&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251211/MXX9ubQFCqeb0HoGBeRC613602146_00_01MXX9ubQFCqeb0HoGBeRC.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>2389</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4132,7 +4480,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4142,24 +4490,38 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
-        </is>
-      </c>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>4454</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4167,29 +4529,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>6120</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
@@ -4202,29 +4578,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대웅제약 녹차카테킨 30정 30일분</t>
+          <t>동국 맛있는 샐러드 미니볼 15포 15일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000136&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910891&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5KgtE2Z5pfS6P1gIBIIh600000136_00_005KgtE2Z5pfS6P1gIBIIh.png</t>
-        </is>
-      </c>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260312/tgDz0oHoOLB3gj3BLgFd610910891_00_01tgDz0oHoOLB3gj3BLgFd.png</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>2079</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
@@ -4237,12 +4627,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
+          <t>휴럼 하루한알 침향환 9환 9일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>휴럼</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4252,19 +4642,33 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=985472642&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157094&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250623/yivvMAKVS3Hyi026FPyX985472642_00_00yivvMAKVS3Hyi026FPyX.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260826/o7EiJdX7BYMCuTvEmVmE919157094_00_01o7EiJdX7BYMCuTvEmVmE.jpg</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4272,12 +4676,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>휴럼 하루한알 침향환 9환 9일분</t>
+          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -4287,19 +4691,33 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157094&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253276&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260826/o7EiJdX7BYMCuTvEmVmE919157094_00_01o7EiJdX7BYMCuTvEmVmE.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260422/qm625V7JKEa8Iu7GrFAf987253276_00_01qm625V7JKEa8Iu7GrFAf.jpg</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>563</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4307,7 +4725,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4317,19 +4735,33 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
-        </is>
-      </c>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>6043</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
@@ -4365,6 +4797,20 @@
           <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>5830</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
@@ -4377,12 +4823,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
+          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4392,14 +4838,28 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=985472642&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250623/yivvMAKVS3Hyi026FPyX985472642_00_00yivvMAKVS3Hyi026FPyX.jpg</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1880</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4517,37 +4977,37 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>혈행</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -4574,7 +5034,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -4584,37 +5044,37 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>휴럼</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>안국약품</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>휴럼</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
     </row>
@@ -4626,52 +5086,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>휴럼 하루한알 6년근 고려 홍삼환 9환 9일분</t>
+          <t>휴럼 하루한포 6년근 고려홍삼 5포 5일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>자연관 바이탈 밀크씨슬＆비타민B 4병</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
-        </is>
-      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 녹차카테킨 30정 30일분</t>
+          <t>동국 맛있는 샐러드 미니볼 15포 15일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
+          <t>휴럼 하루한알 침향환 9환 9일분</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 마그네슘 30정 30일분</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
           <t>안국약품 콜린 미오이노시톨 4000 10포</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>휴럼 하루한알 침향환 9환 9일분</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 마그네슘 30정 30일분</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
     </row>
@@ -4683,42 +5143,42 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
+          <t>2,000원</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>2,000원</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>2,000원</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -4816,7 +5276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4863,11 +5323,51 @@
           <t>이미지URL</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>리뷰평점</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>리뷰건수</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>긍정1</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>긍정2</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>긍정3</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>부정1</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>부정2</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>부정3</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4875,29 +5375,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>14,900원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355480ko.jpg?l=ko</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J2" t="n">
+        <v>21944</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
@@ -4910,29 +5422,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>닥터아돌 카테킨 아세로라CD 60정 (+시나모롤키링)/위디어트 히카바이오틱스 하이드록시 시트르산 21포</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>닥터아돌</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>21,900원</t>
+          <t>14,900원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000237815&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023781533ko.png?l=ko</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355480ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>14675</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
@@ -4968,6 +5492,18 @@
           <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0016/A00000016473622ko.png?l=ko</t>
         </is>
       </c>
+      <c r="I4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>15321</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
@@ -5003,6 +5539,18 @@
           <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018726811ko.png?l=ko</t>
         </is>
       </c>
+      <c r="I5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5528</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
@@ -5015,29 +5563,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
+          <t>닥터아돌 카테킨 아세로라CD 60정 (+시나모롤키링)/위디어트 히카바이오틱스 하이드록시 시트르산 21포</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>대원제약</t>
+          <t>닥터아돌</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>21,900원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247884&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000237815&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024788471ko.jpg?l=ko</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023781533ko.png?l=ko</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7493</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
@@ -5050,29 +5610,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>락토핏 골드 트리플 기획 (3개월분)</t>
+          <t>[수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>락토핏</t>
+          <t>대원제약</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21,900원</t>
+          <t>18,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000199062&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247884&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019906245ko.jpg?l=ko</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024788471ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
@@ -5108,6 +5676,18 @@
           <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021854632ko.jpg?l=ko</t>
         </is>
       </c>
+      <c r="I8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>13636</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
@@ -5143,6 +5723,18 @@
           <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
+      <c r="I9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8046</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
@@ -5178,6 +5770,18 @@
           <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
         </is>
       </c>
+      <c r="I10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>456</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
@@ -5190,29 +5794,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 10종 택 1</t>
+          <t>락토핏 골드 트리플 기획 (3개월분)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>씨제이웰케어</t>
+          <t>락토핏</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5,900원</t>
+          <t>21,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000199062&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786106ko.jpg?l=ko</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019906245ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>27643</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5325,7 +5941,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -5382,52 +5998,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>멜라메이트</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>닥터아돌</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>고려은단</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>고려은단</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>대원제약</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>멜라메이트</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>락토핏</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>멜라메이트</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>프로뉴트리션</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>씨제이웰케어</t>
         </is>
       </c>
     </row>
@@ -5439,52 +6055,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>[9월 올영픽] 고려은단 메가도스C 비타민C 3000mg 30포 (+헬로키티 파우치)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>닥터아돌 카테킨 아세로라CD 60정 (+시나모롤키링)/위디어트 히카바이오틱스 하이드록시 시트르산 21포</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>[9월 올영픽] 고려은단 메가도스C 비타민C 3000mg 30포 (+헬로키티 파우치)</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>[수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>[골라담기/신제품] 멜라메이트 구미 타트체리맛/리치백도맛/애플민트맛/2mg 구미</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>락토핏 골드 트리플 기획 (3개월분)</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[골라담기/신제품] 멜라메이트 구미 타트체리맛/리치백도맛/애플민트맛/2mg 구미</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 10종 택 1</t>
         </is>
       </c>
     </row>
@@ -5496,52 +6112,52 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
+          <t>42,900원</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
           <t>14,900원</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>10,900원</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>9,900원</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>21,900원</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>10,900원</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>9,900원</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>18,900원</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>7,900원</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>31,900원</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>39,800원</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>21,900원</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>7,900원</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>31,900원</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>39,800원</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>5,900원</t>
         </is>
       </c>
     </row>
@@ -5629,7 +6245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5667,45 +6283,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>35</v>
+        <v>27.5</v>
       </c>
       <c r="D2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" t="n">
         <v>3</v>
       </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>27.5</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -5737,10 +6353,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -5749,7 +6365,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -5777,7 +6393,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5790,16 +6406,16 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
         <v>1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5809,10 +6425,10 @@
         <v>2.5</v>
       </c>
       <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
         <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -5821,7 +6437,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5834,16 +6450,16 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
         <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5853,12 +6469,34 @@
         <v>2.5</v>
       </c>
       <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="F10" t="n">
+      <c r="C11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/daily/2026-09/2026-09-08.xlsx
+++ b/data/daily/2026-09/2026-09-08.xlsx
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -5633,8 +5633,12 @@
           <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024788471ko.jpg?l=ko</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5307</v>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -6393,7 +6397,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -6406,10 +6410,10 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
         <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -6459,7 +6463,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -6469,19 +6473,19 @@
         <v>2.5</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -6491,10 +6495,10 @@
         <v>2.5</v>
       </c>
       <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
         <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>

--- a/data/daily/2026-09/2026-09-08.xlsx
+++ b/data/daily/2026-09/2026-09-08.xlsx
@@ -912,7 +912,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1238250" cy="1238250"/>
@@ -937,7 +937,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1238250" cy="1238250"/>
@@ -962,7 +962,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1238250" cy="1238250"/>
@@ -987,7 +987,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1238250" cy="1238250"/>
@@ -1012,7 +1012,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1238250" cy="1238250"/>
@@ -1037,7 +1037,7 @@
     <from>
       <col>7</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1238250" cy="1238250"/>
@@ -1062,7 +1062,7 @@
     <from>
       <col>8</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1238250" cy="1238250"/>
@@ -1087,7 +1087,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1238250" cy="1238250"/>
@@ -1112,7 +1112,7 @@
     <from>
       <col>10</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1238250" cy="1238250"/>
@@ -1137,7 +1137,7 @@
     <from>
       <col>11</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1238250" cy="1238250"/>
@@ -2596,7 +2596,7 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>15990</v>
+        <v>15991</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -3407,7 +3407,7 @@
     <row r="20" ht="38" customHeight="1">
       <c r="B20" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3415,34 +3415,34 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7556791</t>
+          <t>https://gift.kakao.com/product/12064702</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>1534</v>
+        <v>1</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
@@ -3454,7 +3454,7 @@
     <row r="21" ht="38" customHeight="1">
       <c r="B21" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3462,34 +3462,34 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>33,200원</t>
+          <t>25,900원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12064702</t>
+          <t>https://gift.kakao.com/product/7556791</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>1534</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -3510,21 +3510,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3775,471 +3775,687 @@
     <row r="6">
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>판매가</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>34,000원</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>26,900원</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>105,000원</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>24,000원</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>19,900원</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>52,900원</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>35,000원</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>43,000원</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>15,900원</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>59,800원</t>
-        </is>
+          <t>평점</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>링크</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
+          <t>리뷰수</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>15991</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>15326</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>3340</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>6447</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>8686</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>711</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>1611</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>773</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>2607</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>긍정리뷰</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>플랫폼</t>
-        </is>
-      </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>순위</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>1위</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>2위</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>3위</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>4위</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>5위</t>
-        </is>
-      </c>
-      <c r="H9" s="1" t="inlineStr">
-        <is>
-          <t>6위</t>
-        </is>
-      </c>
-      <c r="I9" s="1" t="inlineStr">
-        <is>
-          <t>7위</t>
-        </is>
-      </c>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>8위</t>
-        </is>
-      </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>9위</t>
-        </is>
-      </c>
-      <c r="L9" s="1" t="inlineStr">
-        <is>
-          <t>10위</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="100" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>다이어트·이너뷰티</t>
-        </is>
-      </c>
+          <t>부정리뷰</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>썸네일</t>
+          <t>판매가</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>34,000원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>26,900원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>105,000원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>24,000원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>19,900원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>52,900원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>35,000원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>43,000원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>15,900원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>59,800원</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>카테고리</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>한끼통살</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>아일로</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>한끼통살</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>셀렉스</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>그레인온</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>삼대오백</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>익스트림</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>뉴트리디데이</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>익스트림</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>알디콤</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="46" customHeight="1">
+          <t>링크</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>플랫폼</t>
+        </is>
+      </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>상품명</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)현미크리스피 닭가슴살 오리지널 1개</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>'3입 증정' "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 3입 추가 증정</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파로저당 단백칩 증정</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>"이게 바로 찐! 초고함량" 액상스틱 L-아르기닌 7000 3박스 [케이스 동봉]</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>1위</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>2위</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>3위</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>4위</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>5위</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="inlineStr">
+        <is>
+          <t>6위</t>
+        </is>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>7위</t>
+        </is>
+      </c>
+      <c r="J13" s="1" t="inlineStr">
+        <is>
+          <t>8위</t>
+        </is>
+      </c>
+      <c r="K13" s="1" t="inlineStr">
+        <is>
+          <t>9위</t>
+        </is>
+      </c>
+      <c r="L13" s="1" t="inlineStr">
+        <is>
+          <t>10위</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="100" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>다이어트·이너뷰티</t>
+        </is>
+      </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>판매가</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>39,900원</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>65,900원</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>49,900원</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>28,900원</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>46,900원</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>17,900원</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>43,900원</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>30,900원</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>25,900원</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>33,200원</t>
+          <t>썸네일</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="1" t="inlineStr">
         <is>
+          <t>카테고리</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>한끼통살</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>아일로</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>한끼통살</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>셀렉스</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>그레인온</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>삼대오백</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>뉴트리디데이</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>알디콤</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>상품명</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)현미크리스피 닭가슴살 오리지널 1개</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>'3입 증정' "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 3입 추가 증정</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파로저당 단백칩 증정</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>"이게 바로 찐! 초고함량" 액상스틱 L-아르기닌 7000 3박스 [케이스 동봉]</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>평점</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>리뷰수</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>729</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>142</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>213</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>1653</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>1894</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>247</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>긍정리뷰</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>부정리뷰</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>판매가</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>39,900원</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>65,900원</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>49,900원</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>28,900원</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>46,900원</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>17,900원</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>43,900원</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>30,900원</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>33,200원</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>25,900원</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="1" t="inlineStr">
+        <is>
           <t>링크</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
@@ -4247,30 +4463,30 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A10:A15"/>
+    <mergeCell ref="A2:A11"/>
+    <mergeCell ref="A14:A23"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId21"/>
@@ -4803,7 +5019,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>5830</v>
+        <v>5831</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -4873,21 +5089,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5138,112 +5354,240 @@
     <row r="6">
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>판매가</t>
+          <t>평점</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="1" t="inlineStr">
         <is>
+          <t>리뷰수</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>621</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>2389</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>4454</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>6120</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>2080</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>563</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>6043</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>5831</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>긍정리뷰</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>부정리뷰</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>판매가</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>2,000원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>2,000원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="1" t="inlineStr">
+        <is>
           <t>링크</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
@@ -5251,19 +5595,19 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="A2:A11"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
@@ -5367,7 +5711,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5375,34 +5719,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>42,900원</t>
+          <t>14,900원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355480ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>21944</v>
+        <v>14675</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -5414,7 +5758,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5422,34 +5766,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>14,900원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355480ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J3" t="n">
-        <v>14675</v>
+        <v>21944</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -5543,7 +5887,7 @@
         <v>4.9</v>
       </c>
       <c r="J5" t="n">
-        <v>5528</v>
+        <v>5529</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -5610,34 +5954,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
+          <t>[올영단독] 칼로 스탑/컨트롤 PLUS 15포 2종</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>대원제약</t>
+          <t>칼로(Kalo)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>10,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247884&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000186228&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024788471ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018622875ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J7" t="n">
-        <v>5307</v>
+        <v>12531</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -5743,7 +6087,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5751,34 +6095,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>[수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>대원제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>39,800원</t>
+          <t>18,900원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247884&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024788471ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>456</v>
+        <v>5307</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -5798,34 +6142,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>락토핏 골드 트리플 기획 (3개월분)</t>
+          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 10종 택 1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>락토핏</t>
+          <t>씨제이웰케어</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21,900원</t>
+          <t>5,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000199062&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019906245ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786106ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>27643</v>
+        <v>17464</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -5846,21 +6190,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5945,47 +6289,47 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>비타민C/항산화</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -6002,52 +6346,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>멜라메이트</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>고려은단</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>닥터아돌</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>칼로(Kalo)</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>멜라메이트</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>고려은단</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>고려은단</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>닥터아돌</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>대원제약</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>멜라메이트</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>프로뉴트리션</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>락토핏</t>
+          <t>씨제이웰케어</t>
         </is>
       </c>
     </row>
@@ -6059,14 +6403,14 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
-        </is>
-      </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
           <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
@@ -6084,139 +6428,247 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
+          <t>[올영단독] 칼로 스탑/컨트롤 PLUS 15포 2종</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>[골라담기/신제품] 멜라메이트 구미 타트체리맛/리치백도맛/애플민트맛/2mg 구미</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
           <t>[수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[골라담기/신제품] 멜라메이트 구미 타트체리맛/리치백도맛/애플민트맛/2mg 구미</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
-        </is>
-      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>락토핏 골드 트리플 기획 (3개월분)</t>
+          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 10종 택 1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>판매가</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>42,900원</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>14,900원</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>10,900원</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>9,900원</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>21,900원</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>18,900원</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>7,900원</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>31,900원</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>39,800원</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>21,900원</t>
-        </is>
+          <t>평점</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>4.8</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="1" t="inlineStr">
         <is>
+          <t>리뷰수</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>14675</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>21944</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>15321</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>5529</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>7493</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>12531</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>13636</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>8046</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>5307</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>17464</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>긍정리뷰</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>부정리뷰</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>판매가</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>14,900원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>42,900원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>10,900원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>9,900원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>21,900원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>10,900원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>7,900원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>31,900원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>18,900원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>5,900원</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="1" t="inlineStr">
+        <is>
           <t>링크</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>바로가기</t>
         </is>
@@ -6224,19 +6676,19 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="A2:A11"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
@@ -6287,45 +6739,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>27.5</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>27.5</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
         <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -6397,7 +6849,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -6419,7 +6871,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -6429,10 +6881,10 @@
         <v>2.5</v>
       </c>
       <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
         <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -6441,7 +6893,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -6485,7 +6937,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -6495,10 +6947,10 @@
         <v>2.5</v>
       </c>
       <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
         <v>1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>

--- a/data/daily/2026-09/2026-09-08.xlsx
+++ b/data/daily/2026-09/2026-09-08.xlsx
@@ -1195,14 +1195,89 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1292,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1342,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,17 +1367,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,110 +1392,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="381000" cy="457200"/>
+    <ext cx="323850" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1450,52 +1450,152 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1503,24 +1603,24 @@
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1528,129 +1628,29 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="866775" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2596,7 +2596,7 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>15991</v>
+        <v>15992</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -2737,7 +2737,7 @@
         <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>6447</v>
+        <v>6448</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -2831,7 +2831,7 @@
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -2878,7 +2878,7 @@
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -3407,7 +3407,7 @@
     <row r="20" ht="38" customHeight="1">
       <c r="B20" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3415,34 +3415,34 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>33,200원</t>
+          <t>25,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12064702</t>
+          <t>https://gift.kakao.com/product/7556791</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>1534</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
@@ -3454,7 +3454,7 @@
     <row r="21" ht="38" customHeight="1">
       <c r="B21" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3462,34 +3462,34 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7556791</t>
+          <t>https://gift.kakao.com/product/12064702</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>1534</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>15991</v>
+        <v>15992</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>15326</v>
@@ -3825,16 +3825,16 @@
         <v>3340</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>6447</v>
+        <v>6448</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>8686</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>773</v>
@@ -4116,12 +4116,12 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
     </row>
@@ -4173,12 +4173,12 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
           <t>알디콤</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>익스트림</t>
         </is>
       </c>
     </row>
@@ -4230,12 +4230,12 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
+          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
           <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
     </row>
@@ -4307,10 +4307,10 @@
         <v>38</v>
       </c>
       <c r="K19" s="3" t="n">
+        <v>1534</v>
+      </c>
+      <c r="L19" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>1534</v>
       </c>
     </row>
     <row r="20">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
+          <t>25,900원</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
           <t>33,200원</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>25,900원</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4590,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4598,36 +4598,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>휴럼 하루한포 6년근 고려홍삼 5포 5일분</t>
+          <t>닥터블릿 멜라드림 30정 30일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157053&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=031930043&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260327/PrU3TzDbYVJKWXoKyRxC919157053_00_01PrU3TzDbYVJKWXoKyRxC.jpg</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260106/ifUNcDpBRic8ZZffJeay031930043_00_03ifUNcDpBRic8ZZffJeay.jpg</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>621</v>
+        <v>1566</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -4639,7 +4637,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4647,36 +4645,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
+          <t>대웅제약 루테인 30정 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000126&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4.7</t>
-        </is>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/u8Kxfk5gV3uvRKBRNTM6600000126_00_00u8Kxfk5gV3uvRKBRNTM6.png</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>2389</v>
+        <v>3788</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -4688,7 +4684,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4696,7 +4692,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4711,21 +4707,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>4454</v>
+        <v>5842</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -4768,13 +4762,11 @@
           <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
+      <c r="I5" t="n">
+        <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>6120</v>
+        <v>6121</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -4794,36 +4786,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>동국 맛있는 샐러드 미니볼 15포 15일분</t>
+          <t>종근당건강 락토핏 골드</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>종근당건강</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910891&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591580521&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260312/tgDz0oHoOLB3gj3BLgFd610910891_00_01tgDz0oHoOLB3gj3BLgFd.png</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4.7</t>
-        </is>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260522/0jgRGoNZEcwwrbTgrqVw591580521_00_000jgRGoNZEcwwrbTgrqVw.jpg</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>2080</v>
+        <v>1552</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -4835,7 +4825,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4843,12 +4833,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>휴럼 하루한알 침향환 9환 9일분</t>
+          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4858,21 +4848,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157094&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000203&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260826/o7EiJdX7BYMCuTvEmVmE919157094_00_01o7EiJdX7BYMCuTvEmVmE.jpg</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4.7</t>
-        </is>
+          <t>https://cdn.daisomall.co.kr/file/PD/20251202/7FdyxsWTlcbRJnDROGoC600000203_00_007FdyxsWTlcbRJnDROGoC.jpg</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>6</v>
+        <v>1453</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -4884,7 +4872,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4892,12 +4880,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
+          <t>대웅제약 어린이 칼슘 마그네슘D 츄어블 60정 30일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -4907,21 +4895,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253276&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000143&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260422/qm625V7JKEa8Iu7GrFAf987253276_00_01qm625V7JKEa8Iu7GrFAf.jpg</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/mx3ripII7mLHu95jzlBA600000143_00_00mx3ripII7mLHu95jzlBA.png</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>4.7</v>
       </c>
       <c r="J8" t="n">
-        <v>563</v>
+        <v>490</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -4933,7 +4919,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4941,12 +4927,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4956,21 +4942,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=985472642&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250623/yivvMAKVS3Hyi026FPyX985472642_00_00yivvMAKVS3Hyi026FPyX.jpg</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>6043</v>
+        <v>1880</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -4982,7 +4966,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4990,12 +4974,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대웅제약 마그네슘 30정 30일분</t>
+          <t>[의약외품][신혜선 PICK] 동국제약 멜라케어 더블 화이트 정 10정 10일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5005,21 +4989,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911058&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260710/ttaHg18AMnzwMvyaF63v610911058_00_00ttaHg18AMnzwMvyaF63v.jpg</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.6</v>
       </c>
       <c r="J10" t="n">
-        <v>5831</v>
+        <v>123</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -5031,7 +5013,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5039,12 +5021,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
+          <t>동국제약 이너케어＆유산균 30캡슐</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5054,21 +5036,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=985472642&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910677&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250623/yivvMAKVS3Hyi026FPyX985472642_00_00yivvMAKVS3Hyi026FPyX.jpg</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250829/mBCVgsNacUdX2MZDROO3610910677_00_00mBCVgsNacUdX2MZDROO3.png</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>1880</v>
+        <v>2595</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -5188,17 +5168,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -5213,27 +5193,27 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
     </row>
@@ -5245,12 +5225,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -5265,32 +5245,32 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>종근당건강</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>안국약품</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>동국제약</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>휴럼</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>익스트림</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>동국제약</t>
         </is>
       </c>
     </row>
@@ -5302,17 +5282,17 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>휴럼 하루한포 6년근 고려홍삼 5포 5일분</t>
+          <t>닥터블릿 멜라드림 30정 30일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
+          <t>대웅제약 루테인 30정 30일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -5322,32 +5302,32 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>동국 맛있는 샐러드 미니볼 15포 15일분</t>
+          <t>종근당건강 락토핏 골드</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>휴럼 하루한알 침향환 9환 9일분</t>
+          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
+          <t>대웅제약 어린이 칼슘 마그네슘D 츄어블 60정 30일분</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 마그네슘 30정 30일분</t>
+          <t>[의약외품][신혜선 PICK] 동국제약 멜라케어 더블 화이트 정 10정 10일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
+          <t>동국제약 이너케어＆유산균 30캡슐</t>
         </is>
       </c>
     </row>
@@ -5357,55 +5337,35 @@
           <t>평점</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>4.7</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>4.7</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>4.7</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
+      <c r="C6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>4.8</v>
       </c>
     </row>
     <row r="7">
@@ -5415,34 +5375,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>621</v>
+        <v>1566</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2389</v>
+        <v>3788</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>4454</v>
+        <v>5842</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>6120</v>
+        <v>6121</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>2080</v>
+        <v>1552</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>6</v>
+        <v>1453</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>563</v>
+        <v>490</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>6043</v>
+        <v>1880</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>5831</v>
+        <v>123</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1880</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="8">
@@ -5487,12 +5447,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -5507,7 +5467,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -5711,7 +5671,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5719,34 +5679,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>14,900원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355480ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J2" t="n">
-        <v>14675</v>
+        <v>21948</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -5758,7 +5718,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5766,34 +5726,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>42,900원</t>
+          <t>14,900원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355480ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>21944</v>
+        <v>14680</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -5840,7 +5800,7 @@
         <v>4.9</v>
       </c>
       <c r="J4" t="n">
-        <v>15321</v>
+        <v>15326</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -5887,7 +5847,7 @@
         <v>4.9</v>
       </c>
       <c r="J5" t="n">
-        <v>5529</v>
+        <v>5531</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -5907,34 +5867,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>닥터아돌 카테킨 아세로라CD 60정 (+시나모롤키링)/위디어트 히카바이오틱스 하이드록시 시트르산 21포</t>
+          <t>[수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>닥터아돌</t>
+          <t>대원제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21,900원</t>
+          <t>18,900원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000237815&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247884&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023781533ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024788471ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>7493</v>
+        <v>5310</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -5981,7 +5941,7 @@
         <v>4.7</v>
       </c>
       <c r="J7" t="n">
-        <v>12531</v>
+        <v>12532</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -6028,7 +5988,7 @@
         <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>13636</v>
+        <v>13641</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -6075,7 +6035,7 @@
         <v>4.9</v>
       </c>
       <c r="J9" t="n">
-        <v>8046</v>
+        <v>8051</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -6095,34 +6055,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
+          <t>코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>대원제약</t>
+          <t>코자아</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>32,900원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247884&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000236755&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024788471ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023675540ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>5307</v>
+        <v>5928</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -6169,7 +6129,7 @@
         <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>17464</v>
+        <v>17471</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -6289,12 +6249,12 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -6346,27 +6306,27 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>멜라메이트</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>고려은단</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>고려은단</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>고려은단</t>
-        </is>
-      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>닥터아돌</t>
+          <t>대원제약</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -6386,7 +6346,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>대원제약</t>
+          <t>코자아</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -6403,14 +6363,14 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>고려은단 비타민C1000 600정 (20개월분)</t>
-        </is>
-      </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
           <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
@@ -6423,7 +6383,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>닥터아돌 카테킨 아세로라CD 60정 (+시나모롤키링)/위디어트 히카바이오틱스 하이드록시 시트르산 21포</t>
+          <t>[수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -6443,7 +6403,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>[수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
+          <t>코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -6459,10 +6419,10 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>4.8</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>4.9</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>4.9</v>
@@ -6471,7 +6431,7 @@
         <v>4.9</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>4.7</v>
@@ -6483,7 +6443,7 @@
         <v>4.9</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>4.8</v>
@@ -6496,34 +6456,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>14675</v>
+        <v>21948</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>21944</v>
+        <v>14680</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>15321</v>
+        <v>15326</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>5529</v>
+        <v>5531</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>7493</v>
+        <v>5310</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>12531</v>
+        <v>12532</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>13636</v>
+        <v>13641</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>8046</v>
+        <v>8051</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>5307</v>
+        <v>5928</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>17464</v>
+        <v>17471</v>
       </c>
     </row>
     <row r="8">
@@ -6568,14 +6528,14 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>42,900원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
           <t>14,900원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>42,900원</t>
-        </is>
-      </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
           <t>10,900원</t>
@@ -6588,7 +6548,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>21,900원</t>
+          <t>18,900원</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -6608,7 +6568,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>32,900원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -6743,16 +6703,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>32.5</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
         <v>6</v>
@@ -6761,20 +6721,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -6783,17 +6743,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -6827,7 +6787,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -6837,10 +6797,10 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -6849,14 +6809,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -6865,26 +6825,26 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -6893,7 +6853,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -6903,10 +6863,10 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
         <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -6915,7 +6875,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -6928,16 +6888,16 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
         <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -6947,10 +6907,10 @@
         <v>2.5</v>
       </c>
       <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
         <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>

--- a/data/daily/2026-09/2026-09-08.xlsx
+++ b/data/daily/2026-09/2026-09-08.xlsx
@@ -2598,10 +2598,26 @@
       <c r="J2" t="n">
         <v>15992</v>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>고급스러운 선물용 포장 — 패키지가 고급스러워 생일이나 명절 선물용으로 적합함</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>간편한 섭취 및 휴대성 — 액상과 정제 조합으로 바쁜 아침이나 출근길에도 간편하게 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>확실한 피로 회복 효과 — 몸이 피로하고 허할 때 섭취 시 피로 회복 및 활력 증진에 도움 됨</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>아쉬운 부직포 포장재 — 부직포 포장의 이음새 구멍이 숭숭 뚫려 있어 활용도가 떨어지고 재활용 상자 포장보다 아쉬움</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
@@ -2645,10 +2661,26 @@
       <c r="J3" t="n">
         <v>15326</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>간편한 올인원 구성 — 정제와 액상이 함께 있는 올인원 구성으로 물 없이도 간편하게 챙겨 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>부담 없는 망고피치 맛 — 액상이 쓰지 않고 맛있는 망고피치 맛이라 거부감 없이 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>체력 보충 및 피로 개선 — 피곤하고 지칠 때 먹으면 에너지가 충전되고 피로 회복 효과를 즉각 느낌</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>알약 크기의 부담감 — 알약을 잘 삼키지 못하는 사람에게는 알약 크기가 살짝 크게 느껴질 수 있음</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
@@ -2692,9 +2724,21 @@
       <c r="J4" t="n">
         <v>3340</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>뛰어난 피로 회복 효과 — 피곤하거나 기운이 없을 때 먹으면 즉시 힘이 나고 피로가 풀림</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>고급스러운 선물 패키지 — 상자 패키지가 깔끔하고 고급스러워 부모님이나 지인 선물용으로 적합함</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>편리한 휴대 및 복용 — 휴대하기 편해 외출 시나 피곤할 때 마시기 용이함</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -2739,10 +2783,26 @@
       <c r="J5" t="n">
         <v>6448</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>맛있는 구미 제형 — 쓴맛이나 약 냄새 없이 달콤한 과일 맛 젤리 형태라 간식처럼 먹을 수 있음</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>물 없는 간편한 섭취 — 구미 타입이라 물 없이도 씹어서 간편하게 복용 가능함</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>예쁜 패키지와 선물성 — 포장이 예쁘고 뜯는 재미가 있어 부모님이나 친구 선물용으로 만족스러움</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>하루 섭취량의 아쉬움 — 젤리가 맛있어서 하루 2개라는 적정 섭취량이 아쉽게 느껴짐</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
@@ -2786,9 +2846,21 @@
       <c r="J6" t="n">
         <v>8686</v>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>빠른 기력 및 피로 회복 — 피로감이 심할 때 섭취 시 에너지가 충전되고 피로 회복이 빠르게 나타남</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>위생적인 개별 포장 — 1회분씩 개별 포장되어 있어 위생적이고 들고 다니기 편리함</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>부담 없는 목넘김 — 알약 크기가 크지 않고 맛도 좋아 삼키기에 부담이 없음</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -2833,9 +2905,21 @@
       <c r="J7" t="n">
         <v>712</v>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>상큼하고 맛있는 맛 — 맛이 상큼하고 맛있어서 거부감 없이 섭취함</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>우수한 휴대성 — 병 크기가 적당하여 가방에 넣고 다니며 피곤할 때 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>체력 보충 및 피로 개선 — 몸이 피로하고 체력이 떨어질 때 먹으면 체력 보충에 도움 됨</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -2880,9 +2964,21 @@
       <c r="J8" t="n">
         <v>1612</v>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>재미있는 섭취 방식 — 버튼을 누르면 분말이 액상에 섞이는 구조라 먹는 재미가 있음</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>고급스러운 디자인 — 패키지가 고급스럽고 깔끔하여 정성 어린 선물용으로 적합함</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>상큼하고 맛있는 음료맛 — 쓰지 않고 음료처럼 상큼하여 맛에 대한 부담이 없음</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -2927,11 +3023,31 @@
       <c r="J9" t="n">
         <v>773</v>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>강력한 피로 회복력 — 컨디션이 바닥났을 때 마시면 피로감이 덜하고 기력이 촉진됨</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>상큼한 오렌지 맛 — 진한 오렌지 맛 액상이라 마시기에 부담이 없음</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>우수한 휴대성 — 가방에 쏙 들어가는 사이즈라 집중 관리가 필요할 때 휴대하기 용이함</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>부담스러운 가격대 — 가격이 다소 비싸 내돈내산 구매 시 고민이 됨</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>용기 내 잔여물 남음 — 액상이 꽤 진하여 용기 바닥에 잔여물이 남으므로 물을 넣어 마셔야 함</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
@@ -2974,9 +3090,21 @@
       <c r="J10" t="n">
         <v>2607</v>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>간편한 올인원 제형 — 액상과 정제가 함께 있어 물 없이 한 번에 영양 보충이 가능함</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>상큼한 레몬 맛 — 비린내나 쓴맛 없이 레몬향이 나 호불호 없이 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>휴대하기 편한 포장 — 개별 포장이 깔끔하여 가방에 챙겨 다니며 먹기 편리함</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -3021,9 +3149,21 @@
       <c r="J11" t="n">
         <v>766</v>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>성별 맞춤 옵션 제공 — 남성용(M)과 여성용(F) 옵션을 선택할 수 있어 맞춤 관리가 가능함</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>고급스러운 포장 디자인 — 패키지 구성이 고급스러워 선물용으로 만족도가 높음</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>피로감 감소 효과 — 꾸준히 먹으면 아침에 피로감이 덜하고 기상 컨디션이 좋아짐</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -3068,10 +3208,26 @@
       <c r="J12" t="n">
         <v>49</v>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>부드럽고 촉촉한 식감 — 닭가슴살 특유의 뻑뻑함이 적고 촉촉하여 먹기 편함</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>다양한 구성과 맛 — 메뉴가 다양하게 들어 있어 매일 먹어도 질리지 않음</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>뛰어난 가성비 — 저렴한 가격에 많은 양을 구매할 수 있어 가성비가 훌륭함</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>배송 중 해동 발생 — 배송 과정에서 제품이 완전히 녹아 도착하는 경우가 있음</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
     </row>
@@ -3115,9 +3271,21 @@
       <c r="J13" t="n">
         <v>729</v>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>화려하고 고급진 포장 — 플리츠백 및 오간자 포장이 매우 예뻐 선물 활용도가 높음</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>상큼한 오렌지 맛 — 오렌지 맛 액상 앰플 형태라 마시기 부담 없음</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>콜라겐·비오틴 병합 케어 — 피부 탄력과 피로 회복을 한 번에 관리할 수 있어 유용함</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -3162,11 +3330,31 @@
       <c r="J14" t="n">
         <v>142</v>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>다채로운 제품 종류 — 소세지, 큐브, 닭다리살 등 종류가 다양하여 지속적인 식단 관리에 용이함</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>촉촉한 육즙 유지 — 전자레인지 조리 후에도 퍽퍽하지 않고 촉촉함이 유지됨</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>유용한 보냉백 증정 — 도시락을 싸 다니기에 편리하고 귀여운 보냉백을 함께 받음</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>다소 짭짤한 간 — 양념의 간이 세고 짭짤하다고 느낄 수 있음</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>증정품 옵션 불일치 — 방송 안내와 다른 디자인의 보냉백이 배송됨</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr"/>
     </row>
     <row r="15" ht="38" customHeight="1">
@@ -3209,9 +3397,21 @@
       <c r="J15" t="n">
         <v>213</v>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>비린 맛 없는 음료 감각 — 단백질 음료 특유의 텁텁함이나 비린 맛이 없고 진한 초코 우유 맛임</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>속 편한 락토프리 성분 — 제로슈가 및 락토프리 제품이라 공복에도 부담 없이 복용 가능함</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>운동 후 간편 단백질 보충 — 운동 직후 필요한 단백질을 맛있고 편리하게 챙길 수 있음</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -3256,10 +3456,26 @@
       <c r="J16" t="n">
         <v>1653</v>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>고소한 군고구마 맛 — 효소 특유의 냄새 대신 군고구마 향이 나 맛있게 먹을 수 있음</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>편안한 소화 및 배변 도움 — 과식 후 섭취하면 속이 편해지고 배변 활동에 도움 됨</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>푸짐한 사은품 구성 — 저렴한 가격 대비 다양한 구성품과 사은품이 함께 제공됨</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>기프티콘 사은품 누락 — 행사 대상 사은품 기프티콘 발송이 누락되어 불편을 겪음</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
     </row>
@@ -3303,9 +3519,21 @@
       <c r="J17" t="n">
         <v>1894</v>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>무색무취의 무부담성 — 맛과 향이 거의 없어 단백질 파우더 등에 섞어 먹기 편함</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>우수한 용해성 — 입자가 고와서 물에 잘 녹고 흡수가 빠름</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>운동 수행 능력 향상 — 운동 전 복용 시 펌핑감과 체력 유지에 큰 도움이 됨</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
@@ -3350,9 +3578,21 @@
       <c r="J18" t="n">
         <v>247</v>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>6200mg 초고함량 — 포당 L-아르기닌 함량이 높아 강력한 부스팅 효과를 줌</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>상큼한 베리 맛 — 맛이 상큼하고 맛하여 부담 없이 즐길 수 있음</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>간편한 스틱 포장 — 짜먹거나 물에 타기 편해 일상에서 챙겨 먹기 유용함</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -3397,9 +3637,21 @@
       <c r="J19" t="n">
         <v>38</v>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>상큼한 레몬 맛 — 역하지 않은 레몬 맛이라 영양제를 잘 못 먹는 사람도 편하게 섭취함</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>편리한 액상 스틱 — 외출 시 챙기기 용이하고 물에 잘 녹아 복용하기 간단함</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>피로 회복 체감 — 공복 섭취 시 아침 피로 회복과 운동 효율 증대에 도움이 됨</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -3444,9 +3696,21 @@
       <c r="J20" t="n">
         <v>1534</v>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>아르기닌·밀크씨슬 복합 구성 — 활력과 간 건강을 동시에 케어할 수 있는 세트 구성임</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>간편한 하루 1회 복용 — 하루 한 번 2정 섭취로 간편하며 알약 크기도 적당하여 삼키기 편함</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>개운한 아침 피로 완화 — 복용 후 아침 일어날 때 개운함이 생기고 피로감이 줄어듦</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
@@ -3491,7 +3755,11 @@
       <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>탁월한 숙취 해소 — 섭취 시 숙취 해소 효과가 매우 확실함</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -3846,37 +4114,114 @@
         <v>766</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>고급스러운 선물용 포장 — 패키지가 고급스러워 생일이나 명절 선물용으로 적합함
+간편한 섭취 및 휴대성 — 액상과 정제 조합으로 바쁜 아침이나 출근길에도 간편하게 섭취 가능함
+확실한 피로 회복 효과 — 몸이 피로하고 허할 때 섭취 시 피로 회복 및 활력 증진에 도움 됨</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>간편한 올인원 구성 — 정제와 액상이 함께 있는 올인원 구성으로 물 없이도 간편하게 챙겨 먹기 좋음
+부담 없는 망고피치 맛 — 액상이 쓰지 않고 맛있는 망고피치 맛이라 거부감 없이 섭취 가능함
+체력 보충 및 피로 개선 — 피곤하고 지칠 때 먹으면 에너지가 충전되고 피로 회복 효과를 즉각 느낌</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>뛰어난 피로 회복 효과 — 피곤하거나 기운이 없을 때 먹으면 즉시 힘이 나고 피로가 풀림
+고급스러운 선물 패키지 — 상자 패키지가 깔끔하고 고급스러워 부모님이나 지인 선물용으로 적합함
+편리한 휴대 및 복용 — 휴대하기 편해 외출 시나 피곤할 때 마시기 용이함</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>맛있는 구미 제형 — 쓴맛이나 약 냄새 없이 달콤한 과일 맛 젤리 형태라 간식처럼 먹을 수 있음
+물 없는 간편한 섭취 — 구미 타입이라 물 없이도 씹어서 간편하게 복용 가능함
+예쁜 패키지와 선물성 — 포장이 예쁘고 뜯는 재미가 있어 부모님이나 친구 선물용으로 만족스러움</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>빠른 기력 및 피로 회복 — 피로감이 심할 때 섭취 시 에너지가 충전되고 피로 회복이 빠르게 나타남
+위생적인 개별 포장 — 1회분씩 개별 포장되어 있어 위생적이고 들고 다니기 편리함
+부담 없는 목넘김 — 알약 크기가 크지 않고 맛도 좋아 삼키기에 부담이 없음</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>상큼하고 맛있는 맛 — 맛이 상큼하고 맛있어서 거부감 없이 섭취함
+우수한 휴대성 — 병 크기가 적당하여 가방에 넣고 다니며 피곤할 때 먹기 좋음
+체력 보충 및 피로 개선 — 몸이 피로하고 체력이 떨어질 때 먹으면 체력 보충에 도움 됨</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>재미있는 섭취 방식 — 버튼을 누르면 분말이 액상에 섞이는 구조라 먹는 재미가 있음
+고급스러운 디자인 — 패키지가 고급스럽고 깔끔하여 정성 어린 선물용으로 적합함
+상큼하고 맛있는 음료맛 — 쓰지 않고 음료처럼 상큼하여 맛에 대한 부담이 없음</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>강력한 피로 회복력 — 컨디션이 바닥났을 때 마시면 피로감이 덜하고 기력이 촉진됨
+상큼한 오렌지 맛 — 진한 오렌지 맛 액상이라 마시기에 부담이 없음
+우수한 휴대성 — 가방에 쏙 들어가는 사이즈라 집중 관리가 필요할 때 휴대하기 용이함</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>간편한 올인원 제형 — 액상과 정제가 함께 있어 물 없이 한 번에 영양 보충이 가능함
+상큼한 레몬 맛 — 비린내나 쓴맛 없이 레몬향이 나 호불호 없이 섭취 가능함
+휴대하기 편한 포장 — 개별 포장이 깔끔하여 가방에 챙겨 다니며 먹기 편리함</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>성별 맞춤 옵션 제공 — 남성용(M)과 여성용(F) 옵션을 선택할 수 있어 맞춤 관리가 가능함
+고급스러운 포장 디자인 — 패키지 구성이 고급스러워 선물용으로 만족도가 높음
+피로감 감소 효과 — 꾸준히 먹으면 아침에 피로감이 덜하고 기상 컨디션이 좋아짐</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>아쉬운 부직포 포장재 — 부직포 포장의 이음새 구멍이 숭숭 뚫려 있어 활용도가 떨어지고 재활용 상자 포장보다 아쉬움</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>알약 크기의 부담감 — 알약을 잘 삼키지 못하는 사람에게는 알약 크기가 살짝 크게 느껴질 수 있음</t>
+        </is>
+      </c>
       <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>하루 섭취량의 아쉬움 — 젤리가 맛있어서 하루 2개라는 적정 섭취량이 아쉽게 느껴짐</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>부담스러운 가격대 — 가격이 다소 비싸 내돈내산 구매 시 고민이 됨
+용기 내 잔여물 남음 — 액상이 꽤 진하여 용기 바닥에 잔여물이 남으므로 물을 넣어 마셔야 함</t>
+        </is>
+      </c>
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
     </row>
@@ -4313,34 +4658,105 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="90" customHeight="1">
       <c r="B20" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr"/>
-      <c r="K20" s="3" t="inlineStr"/>
-      <c r="L20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21">
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>부드럽고 촉촉한 식감 — 닭가슴살 특유의 뻑뻑함이 적고 촉촉하여 먹기 편함
+다양한 구성과 맛 — 메뉴가 다양하게 들어 있어 매일 먹어도 질리지 않음
+뛰어난 가성비 — 저렴한 가격에 많은 양을 구매할 수 있어 가성비가 훌륭함</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>화려하고 고급진 포장 — 플리츠백 및 오간자 포장이 매우 예뻐 선물 활용도가 높음
+상큼한 오렌지 맛 — 오렌지 맛 액상 앰플 형태라 마시기 부담 없음
+콜라겐·비오틴 병합 케어 — 피부 탄력과 피로 회복을 한 번에 관리할 수 있어 유용함</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>다채로운 제품 종류 — 소세지, 큐브, 닭다리살 등 종류가 다양하여 지속적인 식단 관리에 용이함
+촉촉한 육즙 유지 — 전자레인지 조리 후에도 퍽퍽하지 않고 촉촉함이 유지됨
+유용한 보냉백 증정 — 도시락을 싸 다니기에 편리하고 귀여운 보냉백을 함께 받음</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>비린 맛 없는 음료 감각 — 단백질 음료 특유의 텁텁함이나 비린 맛이 없고 진한 초코 우유 맛임
+속 편한 락토프리 성분 — 제로슈가 및 락토프리 제품이라 공복에도 부담 없이 복용 가능함
+운동 후 간편 단백질 보충 — 운동 직후 필요한 단백질을 맛있고 편리하게 챙길 수 있음</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>고소한 군고구마 맛 — 효소 특유의 냄새 대신 군고구마 향이 나 맛있게 먹을 수 있음
+편안한 소화 및 배변 도움 — 과식 후 섭취하면 속이 편해지고 배변 활동에 도움 됨
+푸짐한 사은품 구성 — 저렴한 가격 대비 다양한 구성품과 사은품이 함께 제공됨</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>무색무취의 무부담성 — 맛과 향이 거의 없어 단백질 파우더 등에 섞어 먹기 편함
+우수한 용해성 — 입자가 고와서 물에 잘 녹고 흡수가 빠름
+운동 수행 능력 향상 — 운동 전 복용 시 펌핑감과 체력 유지에 큰 도움이 됨</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>6200mg 초고함량 — 포당 L-아르기닌 함량이 높아 강력한 부스팅 효과를 줌
+상큼한 베리 맛 — 맛이 상큼하고 맛하여 부담 없이 즐길 수 있음
+간편한 스틱 포장 — 짜먹거나 물에 타기 편해 일상에서 챙겨 먹기 유용함</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>상큼한 레몬 맛 — 역하지 않은 레몬 맛이라 영양제를 잘 못 먹는 사람도 편하게 섭취함
+편리한 액상 스틱 — 외출 시 챙기기 용이하고 물에 잘 녹아 복용하기 간단함
+피로 회복 체감 — 공복 섭취 시 아침 피로 회복과 운동 효율 증대에 도움이 됨</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>아르기닌·밀크씨슬 복합 구성 — 활력과 간 건강을 동시에 케어할 수 있는 세트 구성임
+간편한 하루 1회 복용 — 하루 한 번 2정 섭취로 간편하며 알약 크기도 적당하여 삼키기 편함
+개운한 아침 피로 완화 — 복용 후 아침 일어날 때 개운함이 생기고 피로감이 줄어듦</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>탁월한 숙취 해소 — 섭취 시 숙취 해소 효과가 매우 확실함</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
       <c r="B21" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>배송 중 해동 발생 — 배송 과정에서 제품이 완전히 녹아 도착하는 경우가 있음</t>
+        </is>
+      </c>
       <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>다소 짭짤한 간 — 양념의 간이 세고 짭짤하다고 느낄 수 있음
+증정품 옵션 불일치 — 방송 안내와 다른 디자인의 보냉백이 배송됨</t>
+        </is>
+      </c>
       <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>기프티콘 사은품 누락 — 행사 대상 사은품 기프티콘 발송이 누락되어 불편을 겪음</t>
+        </is>
+      </c>
       <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr"/>
@@ -4627,11 +5043,27 @@
       <c r="J2" t="n">
         <v>1566</v>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>빠른 입면 유도 — 복용 후 30~60분 내외로 스르르 잠에 들 수 있도록 유도함</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>뛰어난 가성비 — 저렴한 가격으로 불면 증상을 줄이고 숙면을 돕는 유용한 아이템임</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>복용 후 요란한 꿈 — 섭취 후 잠은 오지만 복잡하고 요란한 꿈을 자꾸 꾸게 됨</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>잦은 새벽 깨어남 — 수면 중 새벽에 자주 깨거나 아침에 몸이 무겁게 느껴질 수 있음</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
@@ -4674,10 +5106,26 @@
       <c r="J3" t="n">
         <v>3788</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>부담 없는 가격대 — 3,000원에 한 달 분량을 구매할 수 있어 가성비가 훌륭함</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>작고 부드러운 캡슐 — 캡슐 크기가 작고 말랑하여 목넘김이 용이함</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>눈 피로감 완화 — 스마트폰이나 컴퓨터 사용 후 눈의 뻑뻑함과 피로가 감소함</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>배송 오발송 위험 — 주문한 상품과 다른 제품이 오배송되는 경우가 발생함</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
@@ -4721,9 +5169,21 @@
       <c r="J4" t="n">
         <v>5842</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>눈 떨림 및 쥐 완화 — 섭취 후 눈 밑 떨림이나 자다 다리에 쥐가 나는 증상이 가라앉음</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>숙면 및 긴장 이완 — 자기 전 복용 시 긴장이 풀리고 수면의 질이 높아짐</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>저렴한 구매 가격 — 3,000원의 저렴한 가격으로 마그네슘을 부담 없이 먹을 수 있음</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -4768,10 +5228,22 @@
       <c r="J5" t="n">
         <v>6121</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>권장량 충족 가성비 — 하루 권장량 100mg을 착한 가격에 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>활력 증진 및 컨디션 개선 — 꾸준히 복용 시 몸이 가벼워지고 일상에 활력이 생김</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>저녁 복용 시 수면 방해 — 저녁에 먹을 경우 수면에 방해가 될 수 있어 점심에 먹는 것을 권장함</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
@@ -4815,10 +5287,22 @@
       <c r="J6" t="n">
         <v>1552</v>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>상큼한 블루베리 맛 — 블루베리 맛이 나 아이들도 거부감 없이 맛있게 먹음</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>쾌변 및 장 건강 도움 — 꾸준히 먹으면 배변 활동이 원활해지고 장이 편안해짐</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>수량 대비 높은 단가 — 17포 기준 5,000원으로 타 쇼핑몰 대량 구매 대비 개당 가격이 저렴하지 않음</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
@@ -4862,10 +5346,22 @@
       <c r="J7" t="n">
         <v>1453</v>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>비린내 없는 식물성 원료 — 미세조류 추출 식물성 원료라 섭취 후에도 냄새가 올라오지 않음</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>대형 제약사의 가성비 — 믿을 수 있는 제약사 제품을 저렴하게 이용할 수 있음</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>크기가 다소 큰 알약 — 캡슐 크기가 조금 큰 편이라 알약 삼키기가 부담스러울 수 있음</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
@@ -4909,10 +5405,26 @@
       <c r="J8" t="n">
         <v>490</v>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>씹어 먹는 츄어블 제형 — 물 없이 편하게 씹어서 복용이 가능함</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>은은한 우유·분유 맛 — 향이나 맛이 강하지 않고 고소한 우유 맛이라 섭취하기 좋음</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>부담 없는 영양 함량 — 어린이용이라 과하지 않은 함량으로 보조제로 부담 없이 복용 가능함</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>제형의 단단함 — 알약의 제형이 다소 딱딱하여 녹여 갉아 먹어야 하는 불편이 있음</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
@@ -4956,9 +5468,21 @@
       <c r="J9" t="n">
         <v>1880</v>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>생리주기 정상화 도움 — 생리불순 시 복용하면 불규칙한 주기가 안정되고 생리가 유도됨</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>부담 없는 레몬 맛 — 시지 않은 레몬 맛이라 편하게 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>합리적인 한 달 가격 — 고가의 이노시톨을 저렴한 가성비로 이용할 수 있음</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -5003,11 +5527,27 @@
       <c r="J10" t="n">
         <v>123</v>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>부담 없는 목넘김 — 알약 형태지만 목넘김에 부담이 없어 매일 챙기기 편함</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>간편한 잡티 관리 — 야외 활동 후 기미나 주근깨 완화 목적으로 복용하기 좋음</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>다소 큰 알약 크기 — 알약이 다소 크다고 느껴질 수 있음</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>10일분의 짧은 용량 — 1통에 10일분만 들어 있어 꾸준히 먹으려면 자주 재구매해야 함</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
@@ -5050,10 +5590,26 @@
       <c r="J11" t="n">
         <v>2595</v>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>여성 고민 완화 체감 — 복용 후 냉이 줄어드는 등 여성 건강 개선 효과를 직접 체감함</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>부드러운 목넘김 — 캡슐 크기가 적당하고 무향이라 삼키기 편함</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>가성비 뛰어난 유산균 — 가격이 저렴하여 매일 부담 없이 꾸준히 먹을 수 있음</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>체감 효과의 차이 — 사람에 따라 초기 복용 시 효과를 크게 느끼지 못할 수 있음</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -5405,39 +5961,128 @@
         <v>2595</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>빠른 입면 유도 — 복용 후 30~60분 내외로 스르르 잠에 들 수 있도록 유도함
+뛰어난 가성비 — 저렴한 가격으로 불면 증상을 줄이고 숙면을 돕는 유용한 아이템임</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>부담 없는 가격대 — 3,000원에 한 달 분량을 구매할 수 있어 가성비가 훌륭함
+작고 부드러운 캡슐 — 캡슐 크기가 작고 말랑하여 목넘김이 용이함
+눈 피로감 완화 — 스마트폰이나 컴퓨터 사용 후 눈의 뻑뻑함과 피로가 감소함</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>눈 떨림 및 쥐 완화 — 섭취 후 눈 밑 떨림이나 자다 다리에 쥐가 나는 증상이 가라앉음
+숙면 및 긴장 이완 — 자기 전 복용 시 긴장이 풀리고 수면의 질이 높아짐
+저렴한 구매 가격 — 3,000원의 저렴한 가격으로 마그네슘을 부담 없이 먹을 수 있음</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>권장량 충족 가성비 — 하루 권장량 100mg을 착한 가격에 섭취 가능함
+활력 증진 및 컨디션 개선 — 꾸준히 복용 시 몸이 가벼워지고 일상에 활력이 생김</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>상큼한 블루베리 맛 — 블루베리 맛이 나 아이들도 거부감 없이 맛있게 먹음
+쾌변 및 장 건강 도움 — 꾸준히 먹으면 배변 활동이 원활해지고 장이 편안해짐</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>비린내 없는 식물성 원료 — 미세조류 추출 식물성 원료라 섭취 후에도 냄새가 올라오지 않음
+대형 제약사의 가성비 — 믿을 수 있는 제약사 제품을 저렴하게 이용할 수 있음</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>씹어 먹는 츄어블 제형 — 물 없이 편하게 씹어서 복용이 가능함
+은은한 우유·분유 맛 — 향이나 맛이 강하지 않고 고소한 우유 맛이라 섭취하기 좋음
+부담 없는 영양 함량 — 어린이용이라 과하지 않은 함량으로 보조제로 부담 없이 복용 가능함</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>생리주기 정상화 도움 — 생리불순 시 복용하면 불규칙한 주기가 안정되고 생리가 유도됨
+부담 없는 레몬 맛 — 시지 않은 레몬 맛이라 편하게 먹기 좋음
+합리적인 한 달 가격 — 고가의 이노시톨을 저렴한 가성비로 이용할 수 있음</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>부담 없는 목넘김 — 알약 형태지만 목넘김에 부담이 없어 매일 챙기기 편함
+간편한 잡티 관리 — 야외 활동 후 기미나 주근깨 완화 목적으로 복용하기 좋음</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>여성 고민 완화 체감 — 복용 후 냉이 줄어드는 등 여성 건강 개선 효과를 직접 체감함
+부드러운 목넘김 — 캡슐 크기가 적당하고 무향이라 삼키기 편함
+가성비 뛰어난 유산균 — 가격이 저렴하여 매일 부담 없이 꾸준히 먹을 수 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>복용 후 요란한 꿈 — 섭취 후 잠은 오지만 복잡하고 요란한 꿈을 자꾸 꾸게 됨
+잦은 새벽 깨어남 — 수면 중 새벽에 자주 깨거나 아침에 몸이 무겁게 느껴질 수 있음</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>배송 오발송 위험 — 주문한 상품과 다른 제품이 오배송되는 경우가 발생함</t>
+        </is>
+      </c>
       <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>저녁 복용 시 수면 방해 — 저녁에 먹을 경우 수면에 방해가 될 수 있어 점심에 먹는 것을 권장함</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>수량 대비 높은 단가 — 17포 기준 5,000원으로 타 쇼핑몰 대량 구매 대비 개당 가격이 저렴하지 않음</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>크기가 다소 큰 알약 — 캡슐 크기가 조금 큰 편이라 알약 삼키기가 부담스러울 수 있음</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>제형의 단단함 — 알약의 제형이 다소 딱딱하여 녹여 갉아 먹어야 하는 불편이 있음</t>
+        </is>
+      </c>
       <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>다소 큰 알약 크기 — 알약이 다소 크다고 느껴질 수 있음
+10일분의 짧은 용량 — 1통에 10일분만 들어 있어 꾸준히 먹으려면 자주 재구매해야 함</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>체감 효과의 차이 — 사람에 따라 초기 복용 시 효과를 크게 느끼지 못할 수 있음</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -5708,8 +6353,16 @@
       <c r="J2" t="n">
         <v>21948</v>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>기본 건강 관리 루틴 — 피로 및 면역 관리를 위해 매일 챙겨 먹기 좋은 필수 비타민C임</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>일상 부스터 효과 — 하루의 에너지를 챙기기 위한 건강 보충제로 유용함</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -5755,10 +6408,26 @@
       <c r="J3" t="n">
         <v>14680</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>빠르고 깊은 수면 유도 — 자기 전 먹으면 뒤척임 없이 깊은 잠에 금방 들게 됨</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>맛있는 구미 제형 — 젤리 제형이라 약이라는 부담 없이 맛있게 먹을 수 있음</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>식물성 성분의 안심감 — 식물성 멜라토닌 원료를 사용하여 안심하고 섭취함</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>취침 전 양치 재실시 — 젤리 형태라 섭취 후 양치를 다시 해야 하는 번거로움이 있음</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
@@ -5802,8 +6471,16 @@
       <c r="J4" t="n">
         <v>15326</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>비타민C와 D 복합 보충 — 면역 관리를 돕는 비타민C와 부족하기 쉬운 비타민D를 한 번에 챙김</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>피로 회복 및 건강 케어 — 바쁜 일상이나 운동 시 피로를 줄이고 이너뷰티를 챙기기 적합함</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -5849,11 +6526,27 @@
       <c r="J5" t="n">
         <v>5531</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>고용량의 확연한 피로 감소 — 3000mg 고용량이라 섭취 후 피로도 감소를 확실히 체감함</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>간편한 개별 가루 스틱 — 가루 형태의 스틱이라 챙겨 다니며 먹기 유용함</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>강한 신맛 — 비타민C 함량이 매우 높아 신맛이 강하게 나타남</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>충분한 수분 섭취 필요 — 고용량이므로 결석 예방을 위해 물을 다량 섭취해야 함</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
@@ -5896,9 +6589,21 @@
       <c r="J6" t="n">
         <v>5310</v>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>수면의 질 개선 — 식물성 라임과피추출물 함유로 숙면을 취하도록 도움</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>수월한 입면 진입 — 한 포 섭취 시 밤에 뒤척이지 않고 빠르게 잠들 수 있음</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>간편하게 마시는 포 형태 — 액상 액체 포 제형이라 간편하게 짜서 마시기 좋음</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -5943,8 +6648,16 @@
       <c r="J7" t="n">
         <v>12532</v>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>칼로리 컷팅 및 다이어트 — 식사 전후로 섭취하여 칼로리를 관리하고 체지방 조절에 도움 됨</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>입터짐 예방 보조 — 운동 시 식욕이 돋거나 입이 터질 때 다이어트 보조제로 유용함</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -5990,10 +6703,26 @@
       <c r="J8" t="n">
         <v>13641</v>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>빠른 숙면 유도 — 잠드는 시간을 줄여주고 새벽에 깨지 않도록 도움</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>맛있는 구미 맛 — 체리, 백도 등 과일 맛으로 부담 없이 간식처럼 먹음</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>당 부담을 줄인 성분 — 자일리톨 단맛 및 로우슈가 옵션으로 부담 없이 즐김</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>섭취 후 양치질 필요 — 젤리 제형이라 밤에 먹은 뒤 다시 양치를 해야 함</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
@@ -6037,8 +6766,16 @@
       <c r="J9" t="n">
         <v>8051</v>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>질과 장 동시 관리 — 장 건강과 질 건강을 함께 케어하는 질유산균 제품임</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>하루 1캡슐 간편 복용 — 하루 한 알만 미지근한 물과 먹으면 되어 관리가 간편함</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -6084,10 +6821,26 @@
       <c r="J10" t="n">
         <v>5928</v>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>개운한 아침 기상 — 수면의 질이 개선되어 아침에 몽롱함 없이 개운하게 기상함</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>입면과 숙면 이중 케어 — 젤리로 빠른 입면을 돕고 드링크로 깊은 잠을 자게 해줌</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>맛있는 포도 맛 — 상큼한 포도 맛 젤리라 거부감 없이 매일 챙겨 먹음</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>취침 전 재양치 번거로움 — 젤리를 취침 직전 먹을 경우 양치를 다시 해야 함</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
@@ -6131,8 +6884,16 @@
       <c r="J11" t="n">
         <v>17471</v>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>뛰어난 가성비 — 커피 한 잔 수준의 저렴한 가격으로 여러 영양제를 이용함</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>비린내 없는 부드러운 목넘김 — 오메가3 기준 비린내가 적고 캡슐 크기가 적당하여 삼키기 편함</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -6486,38 +7247,109 @@
         <v>17471</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>기본 건강 관리 루틴 — 피로 및 면역 관리를 위해 매일 챙겨 먹기 좋은 필수 비타민C임
+일상 부스터 효과 — 하루의 에너지를 챙기기 위한 건강 보충제로 유용함</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>빠르고 깊은 수면 유도 — 자기 전 먹으면 뒤척임 없이 깊은 잠에 금방 들게 됨
+맛있는 구미 제형 — 젤리 제형이라 약이라는 부담 없이 맛있게 먹을 수 있음
+식물성 성분의 안심감 — 식물성 멜라토닌 원료를 사용하여 안심하고 섭취함</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>비타민C와 D 복합 보충 — 면역 관리를 돕는 비타민C와 부족하기 쉬운 비타민D를 한 번에 챙김
+피로 회복 및 건강 케어 — 바쁜 일상이나 운동 시 피로를 줄이고 이너뷰티를 챙기기 적합함</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>고용량의 확연한 피로 감소 — 3000mg 고용량이라 섭취 후 피로도 감소를 확실히 체감함
+간편한 개별 가루 스틱 — 가루 형태의 스틱이라 챙겨 다니며 먹기 유용함</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>수면의 질 개선 — 식물성 라임과피추출물 함유로 숙면을 취하도록 도움
+수월한 입면 진입 — 한 포 섭취 시 밤에 뒤척이지 않고 빠르게 잠들 수 있음
+간편하게 마시는 포 형태 — 액상 액체 포 제형이라 간편하게 짜서 마시기 좋음</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>칼로리 컷팅 및 다이어트 — 식사 전후로 섭취하여 칼로리를 관리하고 체지방 조절에 도움 됨
+입터짐 예방 보조 — 운동 시 식욕이 돋거나 입이 터질 때 다이어트 보조제로 유용함</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>빠른 숙면 유도 — 잠드는 시간을 줄여주고 새벽에 깨지 않도록 도움
+맛있는 구미 맛 — 체리, 백도 등 과일 맛으로 부담 없이 간식처럼 먹음
+당 부담을 줄인 성분 — 자일리톨 단맛 및 로우슈가 옵션으로 부담 없이 즐김</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>질과 장 동시 관리 — 장 건강과 질 건강을 함께 케어하는 질유산균 제품임
+하루 1캡슐 간편 복용 — 하루 한 알만 미지근한 물과 먹으면 되어 관리가 간편함</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>개운한 아침 기상 — 수면의 질이 개선되어 아침에 몽롱함 없이 개운하게 기상함
+입면과 숙면 이중 케어 — 젤리로 빠른 입면을 돕고 드링크로 깊은 잠을 자게 해줌
+맛있는 포도 맛 — 상큼한 포도 맛 젤리라 거부감 없이 매일 챙겨 먹음</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>뛰어난 가성비 — 커피 한 잔 수준의 저렴한 가격으로 여러 영양제를 이용함
+비린내 없는 부드러운 목넘김 — 오메가3 기준 비린내가 적고 캡슐 크기가 적당하여 삼키기 편함</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>취침 전 양치 재실시 — 젤리 형태라 섭취 후 양치를 다시 해야 하는 번거로움이 있음</t>
+        </is>
+      </c>
       <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>강한 신맛 — 비타민C 함량이 매우 높아 신맛이 강하게 나타남
+충분한 수분 섭취 필요 — 고용량이므로 결석 예방을 위해 물을 다량 섭취해야 함</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>섭취 후 양치질 필요 — 젤리 제형이라 밤에 먹은 뒤 다시 양치를 해야 함</t>
+        </is>
+      </c>
       <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>취침 전 재양치 번거로움 — 젤리를 취침 직전 먹을 경우 양치를 다시 해야 함</t>
+        </is>
+      </c>
       <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
@@ -6787,7 +7619,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -6800,16 +7632,16 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -6822,10 +7654,10 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -6853,7 +7685,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -6863,10 +7695,10 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
         <v>1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -6875,7 +7707,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -6885,10 +7717,10 @@
         <v>2.5</v>
       </c>
       <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
         <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
